--- a/approaches/examples/EXAMPLES_SUMMARY.xlsx
+++ b/approaches/examples/EXAMPLES_SUMMARY.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -505,8 +505,15 @@
       <c r="E2" t="n">
         <v>2025</v>
       </c>
-      <c r="F2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
+      <c r="F2" s="2" t="n">
+        <v>31342.5614</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>24732.44019216335</v>
+      </c>
       <c r="I2" s="2" t="n"/>
       <c r="J2" t="inlineStr">
         <is>
@@ -517,67 +524,331 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Olive Oil</t>
+          <t>Gaming Consoles</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Food &amp; Beverages</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>14615.4</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>10495.8</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>9256.9769</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2025</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>8208.176036552992</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>14000</v>
-      </c>
+          <t>Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>approaches\examples\olive-oil</t>
+          <t>approaches\examples\gaming-consoles</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Laptops</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n">
+        <v>630850</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>306726.4806</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>320580.0755551852</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>129900</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>approaches\examples\laptops</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Olive Oil</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Food &amp; Beverages</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>14615.4</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>15556.4312</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>23655.3358</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>12651.27145310509</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>15670</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>approaches\examples\olive-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Smartphones</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>557000</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>272825.0049</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>465071.9808</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>226395.562307821</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>approaches\examples\smartphones</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Smartwatches</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>42000</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>22875.001</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>26398.7588</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>65359.09469910082</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>7500</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>approaches\examples\smartwatches</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Tablets</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n">
+        <v>29159.9999</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>48096</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>88434.50040582159</v>
+      </c>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>approaches\examples\tablets</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Televisions</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>7800</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>64790</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>90368.4961</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>98929.24626401761</v>
+      </c>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>approaches\examples\televisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Urea Fertilizer</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Agriculture &amp; Chemicals</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C10" s="2" t="n">
         <v>31241.6</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D10" s="2" t="n">
         <v>55314.7</v>
       </c>
-      <c r="E4" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" t="inlineStr">
+      <c r="E10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" t="inlineStr">
         <is>
           <t>approaches\examples\urea-fertilizer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Watches</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>69100</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>114825</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>40358.322</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>77984.22255599459</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>118900</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>approaches\examples\watches</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Wireless Earbuds</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>approaches\examples\wireless-earbuds</t>
         </is>
       </c>
     </row>

--- a/approaches/examples/EXAMPLES_SUMMARY.xlsx
+++ b/approaches/examples/EXAMPLES_SUMMARY.xlsx
@@ -533,10 +533,24 @@
         </is>
       </c>
       <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
+      <c r="D3" s="2" t="n">
+        <v>11205</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>18569.2811</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>99711.70787182574</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>54550</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>approaches\examples\gaming-consoles</t>
@@ -842,8 +856,18 @@
         </is>
       </c>
       <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
+      <c r="D12" s="2" t="n">
+        <v>15328.001</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>12160.0456</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2025</v>
+      </c>
       <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="n"/>
       <c r="J12" t="inlineStr">
